--- a/src/test/resources/TestSpouseData.xlsx
+++ b/src/test/resources/TestSpouseData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MariiaCherniak\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MariiaCherniak\Documents\GitHub\new\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1754AD8E-5CC7-46B9-9349-C4EC46E75E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E24196-FB0A-4E71-9BFB-114430EC0BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1797C28A-96E6-48B4-9B25-A0996C03259C}"/>
   </bookViews>
@@ -485,7 +485,7 @@
         <v>0</v>
       </c>
       <c r="E1" s="2">
-        <v>319507885</v>
+        <v>319507886</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
